--- a/public/templates/preventivo-template.xlsx
+++ b/public/templates/preventivo-template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56AA19C-E38E-4588-9863-89A94EF78334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D75D51-1B55-4126-8D8C-875C5FE78AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="720" windowWidth="17745" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="0" windowWidth="19320" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Preventivo" sheetId="1" r:id="rId1"/>
@@ -930,12 +930,11 @@
       <c r="F58" s="14"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
@@ -956,7 +955,7 @@
       <c r="F65" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="A65:F65"/>
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="A4:F4"/>
@@ -969,9 +968,8 @@
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A64:F64"/>
     <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A59:F59"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" useFirstPageNumber="1" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
 </worksheet>
 </file>